--- a/experiments/results/resnet34/CIFAR-10/ReAct/standard/results.xlsx
+++ b/experiments/results/resnet34/CIFAR-10/ReAct/standard/results.xlsx
@@ -353,7 +353,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O4"/>
+  <dimension ref="A1:O5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="61.33203125" customWidth="1" style="3" min="15" max="15"/>
@@ -568,6 +568,55 @@
       <c r="O4" s="5" t="inlineStr">
         <is>
           <t>dice_p=None,ash_p=None,react_th=1.0,scale_th=None,type=avg</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="n">
+        <v>35.57</v>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>93.52</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>37.09</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>92.87</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>97.04000000000001</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>41.58</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>93.34999999999999</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>99.03</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>15.83</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>97.38</v>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>25.51</v>
+      </c>
+      <c r="N5" s="5" t="n">
+        <v>95.53</v>
+      </c>
+      <c r="O5" s="5" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=None,react_th=1.1,scale_th=None,type=avg</t>
         </is>
       </c>
     </row>
